--- a/data/projects/drum/raw/드럼POC_샘플.xlsx
+++ b/data/projects/drum/raw/드럼POC_샘플.xlsx
@@ -429,13 +429,13 @@
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="152" customWidth="1" min="1" max="1"/>
+    <col width="270" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>POC 이슈로그 — 필수 5필드(이슈ID·고장모드·심각도·원인분류·상태), 나머지 선택. docs/RECORD_SCHEMA.md 참조</t>
+          <t>POC 이슈로그 — 필수 5필드(이슈ID·고장모드·심각도·원인분류·상태), 나머지 선택. 종결일을 적으면 수렴 추이(발견 vs 종결), 무발생검증(n/목표Cy)을 적으면 폐루프 진행이 표시된다. docs/RECORD_SCHEMA.md 참조</t>
         </is>
       </c>
     </row>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,9 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -496,10 +498,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>종결일</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>무발생검증</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>상세</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>사진(파일명)</t>
         </is>
@@ -538,10 +550,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>비전 오인식 — 재현 조건·로그 기록</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>저조도에서 드럼 마킹 오인식 → 노출 파라미터 보정</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -551,7 +569,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>비전 오인식</t>
+          <t>체결 토크 이탈</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -571,15 +589,21 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>비전 오인식 — 재현 조건·로그 기록</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>토크 상한 파라미터 오설정 → 레시피 수정</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -589,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>비전 오인식</t>
+          <t>전장 간섭</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -609,15 +633,21 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>비전 오인식 — 재현 조건·로그 기록</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>임시 배선 간섭 (시험환경) — 정리 후 미재현</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -637,25 +667,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>시험환경</t>
+          <t>구현(SW)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>검증중</t>
+          <t>종결</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>비전 오인식 — 재현 조건·로그 기록</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>동일 모드 재발 — 역광 조건 한정 재현 → 조명 후드 1차 개선</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -665,35 +701,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>비전 오인식</t>
+          <t>그리퍼 파지 실패</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>설계</t>
+          <t>구현(SW)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>조치중</t>
+          <t>종결</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>비전 오인식 — 재현 조건·로그 기록</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>파지 좌표 오프셋 → 티칭 보정</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -703,17 +745,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>체결 토크 이탈</t>
+          <t>비전 오인식</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>구현(SW)</t>
+          <t>시험환경</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -723,15 +765,21 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>체결 토크 이탈 — 재현 조건·로그 기록</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>랩 조명 교체 공사 영향 (시험환경) — 환경 복구 후 미재현</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -741,17 +789,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>체결 토크 이탈</t>
+          <t>통신 지연</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>구현(SW)</t>
+          <t>설계</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -761,15 +809,21 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>체결 토크 이탈 — 재현 조건·로그 기록</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>PLC 핸드셰이크 타임아웃 여유 부족 → 설계값 조정</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -784,30 +838,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>설계</t>
+          <t>구현(SW)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>검증중</t>
+          <t>종결</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>체결 토크 이탈 — 재현 조건·로그 기록</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>토크 프로파일 과도구간 이탈 → 램프업 로직 수정</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -817,35 +877,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>체결 토크 이탈</t>
+          <t>로그 유실</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>설계</t>
+          <t>구현(SW)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>조치중</t>
+          <t>종결</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>체결 토크 이탈 — 재현 조건·로그 기록</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>버퍼 오버플로 → 플러시 주기 수정</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -855,7 +921,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>그리퍼 파지 실패</t>
+          <t>자재 급송 지연</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -865,7 +931,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>구현(SW)</t>
+          <t>설계</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -875,15 +941,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>그리퍼 파지 실패 — 재현 조건·로그 기록</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>급송 슈트 각도 미세 조정 (설계)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -913,15 +985,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>그리퍼 파지 실패 — 재현 조건·로그 기록</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>동일 모드 재발 — 접근 속도 프로파일 수정</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -931,7 +1009,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>그리퍼 파지 실패</t>
+          <t>비전 오인식</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -941,25 +1019,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>설계</t>
+          <t>시험환경</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>조치중</t>
+          <t>검증중</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>그리퍼 파지 실패 — 재현 조건·로그 기록</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>38/50Cy</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>외란광 유입 각도 한정 재현 → 후드 연장 적용, 무발생 감시 중</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -969,12 +1053,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>통신 지연</t>
+          <t>체결 토크 이탈</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -984,20 +1068,26 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>종결</t>
+          <t>검증중</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>통신 지연 — 재현 조건·로그 기록</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>41/50Cy</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>반력 편차로 상한 근접 — 토크 암 강성 보강(설계) 후 검증 런</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1007,7 +1097,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>통신 지연</t>
+          <t>소음 초과</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1022,20 +1112,26 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>조치중</t>
+          <t>검증중</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>통신 지연 — 재현 조건·로그 기록</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>45/50Cy</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>고속 구간 공진음 → 속도 프로파일 보정, 무발생 감시 중</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1045,35 +1141,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>전장 간섭</t>
+          <t>체결 토크 이탈</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>시험환경</t>
+          <t>설계</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>종결</t>
+          <t>조치중</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>전장 간섭 — 재현 조건·로그 기록</t>
-        </is>
-      </c>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>체결 자세 편차 기인 추정 — 지그 재설계 협의 중</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1083,12 +1181,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>자재 급송 지연</t>
+          <t>비전 오인식</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1098,20 +1196,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>종결</t>
+          <t>조치중</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>자재 급송 지연 — 재현 조건·로그 기록</t>
-        </is>
-      </c>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>고반사 드럼 한정 오인식 → 편광 필터 설계 검토 중</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1121,35 +1221,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>소음 초과</t>
+          <t>그리퍼 파지 실패</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>구현(SW)</t>
+          <t>설계</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>검증중</t>
+          <t>조치중</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>소음 초과 — 재현 조건·로그 기록</t>
-        </is>
-      </c>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>드럼 림 변형품 파지 불가 → 핑거 형상 변경 설계 진행</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1159,7 +1261,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>로그 유실</t>
+          <t>통신 지연</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1174,20 +1276,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>종결</t>
+          <t>조치중</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>로그 유실 — 재현 조건·로그 기록</t>
-        </is>
-      </c>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>로그 폭주 시 지연 재현 → 로그 레벨 조정 적용 중</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
